--- a/lab-standards/BITAC-lab-standard.xlsx
+++ b/lab-standards/BITAC-lab-standard.xlsx
@@ -562,6 +562,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -575,6 +579,10 @@
 Workshop : 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -644,7 +652,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -666,7 +676,9 @@
       <c r="C17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -688,7 +700,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -710,7 +724,9 @@
       <c r="C19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -732,7 +748,9 @@
       <c r="C20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -754,7 +772,9 @@
       <c r="C21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -776,7 +796,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -798,7 +820,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -820,7 +844,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -842,7 +868,9 @@
       <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -864,7 +892,9 @@
       <c r="C26" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -886,7 +916,9 @@
       <c r="C27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -908,7 +940,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -930,7 +964,9 @@
       <c r="C29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -952,7 +988,9 @@
       <c r="C30" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -974,7 +1012,9 @@
       <c r="C31" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -996,7 +1036,9 @@
       <c r="C32" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1018,7 +1060,9 @@
       <c r="C33" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1040,7 +1084,9 @@
       <c r="C34" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -1062,7 +1108,9 @@
       <c r="C35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1084,7 +1132,9 @@
       <c r="C36" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>8</v>
       </c>
@@ -1106,7 +1156,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -1128,7 +1180,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -1274,6 +1328,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1287,6 +1345,10 @@
 Workshop/ lab – 1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1356,7 +1418,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1378,7 +1442,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1400,7 +1466,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1422,7 +1490,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1444,7 +1514,9 @@
       <c r="C20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1466,7 +1538,9 @@
       <c r="C21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1488,7 +1562,9 @@
       <c r="C22" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -1510,7 +1586,9 @@
       <c r="C23" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -1532,7 +1610,9 @@
       <c r="C24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -1554,7 +1634,9 @@
       <c r="C25" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -1576,7 +1658,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -1598,7 +1682,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -1620,7 +1706,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -1642,7 +1730,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -1664,7 +1754,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -1686,7 +1778,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -1708,7 +1802,9 @@
       <c r="C32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1730,7 +1826,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1752,7 +1850,9 @@
       <c r="C34" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -1774,7 +1874,9 @@
       <c r="C35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1920,6 +2022,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1933,6 +2039,10 @@
 Workshop/ lab – 1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2002,7 +2112,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2024,7 +2136,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2046,7 +2160,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -2068,7 +2184,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -2090,7 +2208,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -2112,7 +2232,9 @@
       <c r="C21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>10</v>
       </c>
@@ -2134,7 +2256,9 @@
       <c r="C22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2156,7 +2280,9 @@
       <c r="C23" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2178,7 +2304,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2200,7 +2328,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -2222,7 +2352,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -2244,7 +2376,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -2266,7 +2400,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -2288,7 +2424,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -2310,7 +2448,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -2332,7 +2472,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -2354,7 +2496,9 @@
       <c r="C32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -2376,7 +2520,9 @@
       <c r="C33" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -2398,7 +2544,9 @@
       <c r="C34" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -2544,6 +2692,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2557,6 +2709,10 @@
 Workshop/ lab – 1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2626,7 +2782,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2648,7 +2806,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2670,7 +2830,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -2692,7 +2854,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -2714,7 +2878,9 @@
       <c r="C20" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -2736,7 +2902,9 @@
       <c r="C21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -2758,7 +2926,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2780,7 +2950,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -2802,7 +2974,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -2824,7 +2998,9 @@
       <c r="C25" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -2846,7 +3022,9 @@
       <c r="C26" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -2868,7 +3046,9 @@
       <c r="C27" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -2890,7 +3070,9 @@
       <c r="C28" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -2912,7 +3094,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -2934,7 +3118,9 @@
       <c r="C30" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -2956,7 +3142,9 @@
       <c r="C31" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -2978,7 +3166,9 @@
       <c r="C32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>9</v>
       </c>
@@ -3000,7 +3190,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>8</v>
       </c>
@@ -3022,7 +3214,9 @@
       <c r="C34" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -3044,7 +3238,9 @@
       <c r="C35" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>5</v>
       </c>
@@ -3066,7 +3262,9 @@
       <c r="C36" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -3088,7 +3286,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -3110,7 +3310,9 @@
       <c r="C38" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>7</v>
       </c>
@@ -3132,7 +3334,9 @@
       <c r="C39" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>7</v>
       </c>
@@ -3154,7 +3358,9 @@
       <c r="C40" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>7</v>
       </c>
@@ -3176,7 +3382,9 @@
       <c r="C41" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>7</v>
       </c>
@@ -3198,7 +3406,9 @@
       <c r="C42" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>4</v>
       </c>
@@ -3220,7 +3430,9 @@
       <c r="C43" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>7</v>
       </c>
@@ -3242,7 +3454,9 @@
       <c r="C44" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>8</v>
       </c>
@@ -3264,7 +3478,9 @@
       <c r="C45" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>7</v>
       </c>
@@ -3286,7 +3502,9 @@
       <c r="C46" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>6</v>
       </c>
@@ -3308,7 +3526,9 @@
       <c r="C47" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="9" t="n">
         <v>5</v>
       </c>
@@ -3330,7 +3550,9 @@
       <c r="C48" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D48" s="9" t="n"/>
+      <c r="D48" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="9" t="n">
         <v>5</v>
       </c>
@@ -3352,7 +3574,9 @@
       <c r="C49" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D49" s="9" t="n"/>
+      <c r="D49" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="9" t="n">
         <v>7</v>
       </c>
@@ -3374,7 +3598,9 @@
       <c r="C50" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D50" s="9" t="n"/>
+      <c r="D50" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" s="9" t="n">
         <v>8</v>
       </c>
@@ -3396,7 +3622,9 @@
       <c r="C51" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D51" s="9" t="n"/>
+      <c r="D51" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" s="9" t="n">
         <v>7</v>
       </c>
@@ -3418,7 +3646,9 @@
       <c r="C52" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D52" s="9" t="n"/>
+      <c r="D52" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" s="9" t="n">
         <v>6</v>
       </c>
@@ -3440,7 +3670,9 @@
       <c r="C53" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D53" s="9" t="n"/>
+      <c r="D53" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E53" s="9" t="n">
         <v>7</v>
       </c>
@@ -3462,7 +3694,9 @@
       <c r="C54" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D54" s="9" t="n"/>
+      <c r="D54" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E54" s="9" t="n">
         <v>5</v>
       </c>
@@ -3484,7 +3718,9 @@
       <c r="C55" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D55" s="9" t="n"/>
+      <c r="D55" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E55" s="9" t="n">
         <v>5</v>
       </c>
@@ -3506,7 +3742,9 @@
       <c r="C56" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="9" t="n"/>
+      <c r="D56" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E56" s="9" t="n">
         <v>6</v>
       </c>
@@ -3652,6 +3890,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3665,6 +3907,10 @@
 Workshop : 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3734,7 +3980,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3756,7 +4004,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
@@ -3778,7 +4028,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3800,7 +4052,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -3822,7 +4076,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -3844,7 +4100,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -3866,7 +4124,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -3888,7 +4148,9 @@
       <c r="C23" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -3910,7 +4172,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -3932,7 +4196,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>9</v>
       </c>
@@ -3954,7 +4220,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -3976,7 +4244,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -3998,7 +4268,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -4020,7 +4292,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -4042,7 +4316,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -4064,7 +4340,9 @@
       <c r="C31" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -4086,7 +4364,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -4108,7 +4388,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -4130,7 +4412,9 @@
       <c r="C34" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -4152,7 +4436,9 @@
       <c r="C35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -4298,6 +4584,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4311,6 +4601,10 @@
 CNC Workshop : 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4380,7 +4674,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -4402,7 +4698,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -4424,7 +4722,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -4446,7 +4746,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -4468,7 +4770,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -4490,7 +4794,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -4512,7 +4818,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -4534,7 +4842,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -4556,7 +4866,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -4702,6 +5014,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4715,6 +5031,10 @@
 Workshop : 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4784,7 +5104,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -4806,7 +5128,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
@@ -4828,7 +5152,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -4850,7 +5176,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -4872,7 +5200,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -4894,7 +5224,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -4916,7 +5248,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -4938,7 +5272,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -4960,7 +5296,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -4982,7 +5320,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>10</v>
       </c>
@@ -5004,7 +5344,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>9</v>
       </c>
@@ -5026,7 +5368,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -5048,7 +5392,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -5070,7 +5416,9 @@
       <c r="C29" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -5092,7 +5440,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -5114,7 +5464,9 @@
       <c r="C31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -5136,7 +5488,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
